--- a/tests/fixtures/2020-2025 SDN Conflict-Related Sexual Violence (CRSV) Incident Data.xlsx
+++ b/tests/fixtures/2020-2025 SDN Conflict-Related Sexual Violence (CRSV) Incident Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4694" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="419">
   <si>
     <t>Date</t>
   </si>
@@ -401,18 +401,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unspecified Sexual Violence </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>120352</t>
@@ -1754,7 +1742,7 @@
         <v>25</v>
       </c>
       <c r="V2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="W2" s="1">
         <v>45988</v>
@@ -1822,7 +1810,7 @@
         <v>3</v>
       </c>
       <c r="V3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="W3" s="1">
         <v>45979</v>
@@ -1890,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="W4" s="1">
         <v>45979</v>
@@ -1958,7 +1946,7 @@
         <v>2</v>
       </c>
       <c r="V5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="W5" s="1">
         <v>45979</v>
@@ -2026,7 +2014,7 @@
         <v>3</v>
       </c>
       <c r="V6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="W6" s="1">
         <v>45979</v>
@@ -2094,7 +2082,7 @@
         <v>2</v>
       </c>
       <c r="V7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="W7" s="1">
         <v>45979</v>
@@ -2162,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="W8" s="1">
         <v>45957</v>
@@ -2230,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="V9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="W9" s="1">
         <v>45956</v>
@@ -2298,7 +2286,7 @@
         <v>2</v>
       </c>
       <c r="V10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="W10" s="1">
         <v>45942</v>
@@ -2366,7 +2354,7 @@
         <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="W11" s="1">
         <v>45903</v>
@@ -2434,7 +2422,7 @@
         <v>95</v>
       </c>
       <c r="V12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="W12" s="1">
         <v>45870</v>
@@ -2502,7 +2490,7 @@
         <v>3</v>
       </c>
       <c r="V13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="W13" s="1">
         <v>45864</v>
@@ -2570,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="V14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="W14" s="1">
         <v>45864</v>
@@ -2638,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="W15" s="1">
         <v>45856</v>
@@ -2705,11 +2693,11 @@
       <c r="T16">
         <v>2</v>
       </c>
-      <c r="U16" t="s">
-        <v>129</v>
+      <c r="U16">
+        <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="W16" s="1">
         <v>45858</v>
@@ -2776,11 +2764,11 @@
       <c r="T17">
         <v>10</v>
       </c>
-      <c r="U17" t="s">
-        <v>130</v>
+      <c r="U17">
+        <v>3</v>
       </c>
       <c r="V17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="W17" s="1">
         <v>45856</v>
@@ -2848,7 +2836,7 @@
         <v>30</v>
       </c>
       <c r="V18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="W18" s="1">
         <v>45856</v>
@@ -2915,11 +2903,11 @@
       <c r="T19">
         <v>1</v>
       </c>
-      <c r="U19" t="s">
-        <v>129</v>
+      <c r="U19">
+        <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="W19" s="1">
         <v>45856</v>
@@ -2987,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="V20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="W20" s="1">
         <v>45854</v>
@@ -3055,7 +3043,7 @@
         <v>5</v>
       </c>
       <c r="V21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="W21" s="1">
         <v>45903</v>
@@ -3123,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="W22" s="1">
         <v>45818</v>
@@ -3191,7 +3179,7 @@
         <v>3</v>
       </c>
       <c r="V23" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="W23" s="1">
         <v>45817</v>
@@ -3259,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="W24" s="1">
         <v>45858</v>
@@ -3327,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="V25" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="W25" s="1">
         <v>45858</v>
@@ -3395,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="W26" s="1">
         <v>45858</v>
@@ -3463,7 +3451,7 @@
         <v>2</v>
       </c>
       <c r="V27" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="W27" s="1">
         <v>45818</v>
@@ -3531,7 +3519,7 @@
         <v>8</v>
       </c>
       <c r="V28" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="W28" s="1">
         <v>45817</v>
@@ -3599,7 +3587,7 @@
         <v>4</v>
       </c>
       <c r="V29" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="W29" s="1">
         <v>45817</v>
@@ -3667,7 +3655,7 @@
         <v>2</v>
       </c>
       <c r="V30" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="W30" s="1">
         <v>45807</v>
@@ -3735,7 +3723,7 @@
         <v>2</v>
       </c>
       <c r="V31" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="W31" s="1">
         <v>45807</v>
@@ -3803,7 +3791,7 @@
         <v>5</v>
       </c>
       <c r="V32" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="W32" s="1">
         <v>45807</v>
@@ -3871,7 +3859,7 @@
         <v>2</v>
       </c>
       <c r="V33" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="W33" s="1">
         <v>45744</v>
@@ -3939,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="V34" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="W34" s="1">
         <v>45744</v>
@@ -4007,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="V35" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="W35" s="1">
         <v>45744</v>
@@ -4075,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="V36" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="W36" s="1">
         <v>45795</v>
@@ -4143,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="V37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W37" s="1">
         <v>45744</v>
@@ -4211,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W38" s="1">
         <v>45744</v>
@@ -4279,7 +4267,7 @@
         <v>2</v>
       </c>
       <c r="V39" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W39" s="1">
         <v>45744</v>
@@ -4347,7 +4335,7 @@
         <v>3</v>
       </c>
       <c r="V40" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="W40" s="1">
         <v>45753</v>
@@ -4415,7 +4403,7 @@
         <v>3</v>
       </c>
       <c r="V41" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="W41" s="1">
         <v>45792</v>
@@ -4482,11 +4470,11 @@
       <c r="T42">
         <v>2</v>
       </c>
-      <c r="U42" t="s">
-        <v>129</v>
+      <c r="U42">
+        <v>1</v>
       </c>
       <c r="V42" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="W42" s="1">
         <v>45709</v>
@@ -4553,11 +4541,11 @@
       <c r="T43">
         <v>1</v>
       </c>
-      <c r="U43" t="s">
-        <v>129</v>
+      <c r="U43">
+        <v>1</v>
       </c>
       <c r="V43" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="W43" s="1">
         <v>45726</v>
@@ -4625,7 +4613,7 @@
         <v>2</v>
       </c>
       <c r="V44" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="W44" s="1">
         <v>45727</v>
@@ -4693,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="V45" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="W45" s="1">
         <v>45700</v>
@@ -4760,11 +4748,11 @@
       <c r="T46">
         <v>1</v>
       </c>
-      <c r="U46" t="s">
-        <v>129</v>
+      <c r="U46">
+        <v>1</v>
       </c>
       <c r="V46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="W46" s="1">
         <v>45727</v>
@@ -4831,11 +4819,11 @@
       <c r="T47">
         <v>1</v>
       </c>
-      <c r="U47" t="s">
-        <v>129</v>
+      <c r="U47">
+        <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="W47" s="1">
         <v>45697</v>
@@ -4902,11 +4890,11 @@
       <c r="T48">
         <v>1</v>
       </c>
-      <c r="U48" t="s">
-        <v>129</v>
+      <c r="U48">
+        <v>1</v>
       </c>
       <c r="V48" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="W48" s="1">
         <v>45690</v>
@@ -4974,7 +4962,7 @@
         <v>2</v>
       </c>
       <c r="V49" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="W49" s="1">
         <v>45697</v>
@@ -5042,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="V50" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="W50" s="1">
         <v>45697</v>
@@ -5110,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="V51" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="W51" s="1">
         <v>45697</v>
@@ -5178,7 +5166,7 @@
         <v>2</v>
       </c>
       <c r="V52" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="W52" s="1">
         <v>45697</v>
@@ -5246,7 +5234,7 @@
         <v>21</v>
       </c>
       <c r="V53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="W53" s="1">
         <v>45697</v>
@@ -5313,11 +5301,11 @@
       <c r="T54">
         <v>2</v>
       </c>
-      <c r="U54" t="s">
-        <v>129</v>
+      <c r="U54">
+        <v>1</v>
       </c>
       <c r="V54" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="W54" s="1">
         <v>45646</v>
@@ -5385,7 +5373,7 @@
         <v>1</v>
       </c>
       <c r="V55" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W55" s="1">
         <v>45693</v>
@@ -5453,7 +5441,7 @@
         <v>2</v>
       </c>
       <c r="V56" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="W56" s="1">
         <v>45693</v>
@@ -5521,7 +5509,7 @@
         <v>2</v>
       </c>
       <c r="V57" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="W57" s="1">
         <v>45693</v>
@@ -5589,7 +5577,7 @@
         <v>21</v>
       </c>
       <c r="V58" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="W58" s="1">
         <v>45693</v>
@@ -5656,11 +5644,11 @@
       <c r="T59">
         <v>1</v>
       </c>
-      <c r="U59" t="s">
-        <v>129</v>
+      <c r="U59">
+        <v>1</v>
       </c>
       <c r="V59" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="W59" s="1">
         <v>45693</v>
@@ -5728,7 +5716,7 @@
         <v>2</v>
       </c>
       <c r="V60" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="W60" s="1">
         <v>45693</v>
@@ -5796,7 +5784,7 @@
         <v>4</v>
       </c>
       <c r="V61" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W61" s="1">
         <v>45693</v>
@@ -5864,7 +5852,7 @@
         <v>2</v>
       </c>
       <c r="V62" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="W62" s="1">
         <v>45683</v>
@@ -5932,7 +5920,7 @@
         <v>2</v>
       </c>
       <c r="V63" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W63" s="1">
         <v>45683</v>
@@ -6000,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="V64" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="W64" s="1">
         <v>45683</v>
@@ -6068,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="V65" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="W65" s="1">
         <v>45683</v>
@@ -6136,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="V66" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="W66" s="1">
         <v>45683</v>
@@ -6204,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="V67" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="W67" s="1">
         <v>45683</v>
@@ -6272,7 +6260,7 @@
         <v>2</v>
       </c>
       <c r="V68" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="W68" s="1">
         <v>45630</v>
@@ -6339,11 +6327,11 @@
       <c r="T69">
         <v>1</v>
       </c>
-      <c r="U69" t="s">
-        <v>129</v>
+      <c r="U69">
+        <v>1</v>
       </c>
       <c r="V69" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="W69" s="1">
         <v>45634</v>
@@ -6411,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="V70" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="W70" s="1">
         <v>45630</v>
@@ -6479,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="V71" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="W71" s="1">
         <v>45586</v>
@@ -6547,7 +6535,7 @@
         <v>2</v>
       </c>
       <c r="V72" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="W72" s="1">
         <v>45586</v>
@@ -6614,11 +6602,11 @@
       <c r="T73">
         <v>1</v>
       </c>
-      <c r="U73" t="s">
-        <v>129</v>
+      <c r="U73">
+        <v>1</v>
       </c>
       <c r="V73" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="W73" s="1">
         <v>45586</v>
@@ -6685,11 +6673,11 @@
       <c r="T74">
         <v>1</v>
       </c>
-      <c r="U74" t="s">
-        <v>129</v>
+      <c r="U74">
+        <v>1</v>
       </c>
       <c r="V74" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="W74" s="1">
         <v>45615</v>
@@ -6757,7 +6745,7 @@
         <v>2</v>
       </c>
       <c r="V75" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="W75" s="1">
         <v>45552</v>
@@ -6824,11 +6812,11 @@
       <c r="T76">
         <v>5</v>
       </c>
-      <c r="U76" t="s">
-        <v>131</v>
+      <c r="U76">
+        <v>5</v>
       </c>
       <c r="V76" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="W76" s="1">
         <v>45565</v>
@@ -6896,7 +6884,7 @@
         <v>21</v>
       </c>
       <c r="V77" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="W77" s="1">
         <v>45566</v>
@@ -6963,11 +6951,11 @@
       <c r="T78">
         <v>1</v>
       </c>
-      <c r="U78" t="s">
-        <v>129</v>
+      <c r="U78">
+        <v>1</v>
       </c>
       <c r="V78" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="W78" s="1">
         <v>45565</v>
@@ -7035,7 +7023,7 @@
         <v>5</v>
       </c>
       <c r="V79" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="W79" s="1">
         <v>45564</v>
@@ -7103,7 +7091,7 @@
         <v>4</v>
       </c>
       <c r="V80" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="W80" s="1">
         <v>45564</v>
@@ -7171,7 +7159,7 @@
         <v>2</v>
       </c>
       <c r="V81" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="W81" s="1">
         <v>45565</v>
@@ -7239,7 +7227,7 @@
         <v>3</v>
       </c>
       <c r="V82" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="W82" s="1">
         <v>45528</v>
@@ -7307,7 +7295,7 @@
         <v>3</v>
       </c>
       <c r="V83" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="W83" s="1">
         <v>45942</v>
@@ -7375,7 +7363,7 @@
         <v>1</v>
       </c>
       <c r="V84" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="W84" s="1">
         <v>45528</v>
@@ -7443,7 +7431,7 @@
         <v>2</v>
       </c>
       <c r="V85" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="W85" s="1">
         <v>45528</v>
@@ -7511,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="V86" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="W86" s="1">
         <v>45564</v>
@@ -7578,11 +7566,11 @@
       <c r="T87">
         <v>1</v>
       </c>
-      <c r="U87" t="s">
-        <v>129</v>
+      <c r="U87">
+        <v>1</v>
       </c>
       <c r="V87" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="W87" s="1">
         <v>45504</v>
@@ -7650,7 +7638,7 @@
         <v>2</v>
       </c>
       <c r="V88" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="W88" s="1">
         <v>45505</v>
@@ -7718,7 +7706,7 @@
         <v>2</v>
       </c>
       <c r="V89" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="W89" s="1">
         <v>45505</v>
@@ -7786,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="V90" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="W90" s="1">
         <v>45482</v>
@@ -7854,7 +7842,7 @@
         <v>4</v>
       </c>
       <c r="V91" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="W91" s="1">
         <v>45481</v>
@@ -7922,7 +7910,7 @@
         <v>3</v>
       </c>
       <c r="V92" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W92" s="1">
         <v>45482</v>
@@ -7990,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="V93" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="W93" s="1">
         <v>45450</v>
@@ -8058,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="V94" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="W94" s="1">
         <v>45449</v>
@@ -8126,7 +8114,7 @@
         <v>1</v>
       </c>
       <c r="V95" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="W95" s="1">
         <v>45449</v>
@@ -8194,7 +8182,7 @@
         <v>2</v>
       </c>
       <c r="V96" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="W96" s="1">
         <v>45440</v>
@@ -8262,7 +8250,7 @@
         <v>27</v>
       </c>
       <c r="V97" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="W97" s="1">
         <v>45440</v>
@@ -8330,7 +8318,7 @@
         <v>2</v>
       </c>
       <c r="V98" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="W98" s="1">
         <v>45440</v>
@@ -8398,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="V99" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="W99" s="1">
         <v>45384</v>
@@ -8465,11 +8453,11 @@
       <c r="T100">
         <v>1</v>
       </c>
-      <c r="U100" t="s">
-        <v>129</v>
+      <c r="U100">
+        <v>1</v>
       </c>
       <c r="V100" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="W100" s="1">
         <v>45440</v>
@@ -8536,11 +8524,11 @@
       <c r="T101">
         <v>1</v>
       </c>
-      <c r="U101" t="s">
-        <v>129</v>
+      <c r="U101">
+        <v>1</v>
       </c>
       <c r="V101" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="W101" s="1">
         <v>45374</v>
@@ -8608,7 +8596,7 @@
         <v>12</v>
       </c>
       <c r="V102" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="W102" s="1">
         <v>45374</v>
@@ -8676,7 +8664,7 @@
         <v>2</v>
       </c>
       <c r="V103" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="W103" s="1">
         <v>45440</v>
@@ -8744,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="V104" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="W104" s="1">
         <v>45374</v>
@@ -8812,7 +8800,7 @@
         <v>2</v>
       </c>
       <c r="V105" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="W105" s="1">
         <v>45374</v>
@@ -8879,11 +8867,11 @@
       <c r="T106">
         <v>1</v>
       </c>
-      <c r="U106" t="s">
-        <v>129</v>
+      <c r="U106">
+        <v>1</v>
       </c>
       <c r="V106" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="W106" s="1">
         <v>45564</v>
@@ -8951,7 +8939,7 @@
         <v>2</v>
       </c>
       <c r="V107" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W107" s="1">
         <v>45360</v>
@@ -9019,7 +9007,7 @@
         <v>26</v>
       </c>
       <c r="V108" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="W108" s="1">
         <v>45360</v>
@@ -9087,7 +9075,7 @@
         <v>47</v>
       </c>
       <c r="V109" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="W109" s="1">
         <v>45360</v>
@@ -9155,7 +9143,7 @@
         <v>1</v>
       </c>
       <c r="V110" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W110" s="1">
         <v>45360</v>
@@ -9223,7 +9211,7 @@
         <v>1</v>
       </c>
       <c r="V111" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="W111" s="1">
         <v>45360</v>
@@ -9291,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="V112" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="W112" s="1">
         <v>45360</v>
@@ -9359,7 +9347,7 @@
         <v>2</v>
       </c>
       <c r="V113" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="W113" s="1">
         <v>45308</v>
@@ -9426,11 +9414,11 @@
       <c r="T114">
         <v>1</v>
       </c>
-      <c r="U114" t="s">
-        <v>129</v>
+      <c r="U114">
+        <v>1</v>
       </c>
       <c r="V114" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W114" s="1">
         <v>45308</v>
@@ -9498,7 +9486,7 @@
         <v>2</v>
       </c>
       <c r="V115" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W115" s="1">
         <v>45313</v>
@@ -9565,11 +9553,11 @@
       <c r="T116">
         <v>1</v>
       </c>
-      <c r="U116" t="s">
-        <v>129</v>
+      <c r="U116">
+        <v>1</v>
       </c>
       <c r="V116" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="W116" s="1">
         <v>45307</v>
@@ -9637,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="V117" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="W117" s="1">
         <v>45307</v>
@@ -9705,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="V118" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="W118" s="1">
         <v>45307</v>
@@ -9773,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="V119" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="W119" s="1">
         <v>45339</v>
@@ -9841,7 +9829,7 @@
         <v>4</v>
       </c>
       <c r="V120" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="W120" s="1">
         <v>45305</v>
@@ -9909,7 +9897,7 @@
         <v>2</v>
       </c>
       <c r="V121" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="W121" s="1">
         <v>45339</v>
@@ -9977,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="V122" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="W122" s="1">
         <v>45339</v>
@@ -10045,7 +10033,7 @@
         <v>24</v>
       </c>
       <c r="V123" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="W123" s="1">
         <v>45295</v>
@@ -10113,7 +10101,7 @@
         <v>32</v>
       </c>
       <c r="V124" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="W124" s="1">
         <v>45296</v>
@@ -10181,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="V125" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="W125" s="1">
         <v>45339</v>
@@ -10249,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="V126" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="W126" s="1">
         <v>45262</v>
@@ -10317,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="V127" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W127" s="1">
         <v>45262</v>
@@ -10385,7 +10373,7 @@
         <v>2</v>
       </c>
       <c r="V128" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="W128" s="1">
         <v>45262</v>
@@ -10453,7 +10441,7 @@
         <v>3</v>
       </c>
       <c r="V129" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="W129" s="1">
         <v>45262</v>
@@ -10521,7 +10509,7 @@
         <v>4</v>
       </c>
       <c r="V130" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="W130" s="1">
         <v>45262</v>
@@ -10589,7 +10577,7 @@
         <v>1</v>
       </c>
       <c r="V131" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="W131" s="1">
         <v>45482</v>
@@ -10656,11 +10644,11 @@
       <c r="T132">
         <v>3</v>
       </c>
-      <c r="U132" t="s">
-        <v>130</v>
+      <c r="U132">
+        <v>3</v>
       </c>
       <c r="V132" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="W132" s="1">
         <v>45262</v>
@@ -10728,7 +10716,7 @@
         <v>2</v>
       </c>
       <c r="V133" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="W133" s="1">
         <v>45262</v>
@@ -10795,11 +10783,11 @@
       <c r="T134">
         <v>1</v>
       </c>
-      <c r="U134" t="s">
-        <v>129</v>
+      <c r="U134">
+        <v>1</v>
       </c>
       <c r="V134" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="W134" s="1">
         <v>45262</v>
@@ -10867,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="V135" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="W135" s="1">
         <v>45262</v>
@@ -10935,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="V136" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="W136" s="1">
         <v>45219</v>
@@ -11003,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="V137" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="W137" s="1">
         <v>45219</v>
@@ -11071,7 +11059,7 @@
         <v>5</v>
       </c>
       <c r="V138" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="W138" s="1">
         <v>45262</v>
@@ -11139,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="V139" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="W139" s="1">
         <v>45219</v>
@@ -11207,7 +11195,7 @@
         <v>1</v>
       </c>
       <c r="V140" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="W140" s="1">
         <v>45219</v>
@@ -11275,7 +11263,7 @@
         <v>3</v>
       </c>
       <c r="V141" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="W141" s="1">
         <v>45219</v>
@@ -11343,7 +11331,7 @@
         <v>2</v>
       </c>
       <c r="V142" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="W142" s="1">
         <v>45219</v>
@@ -11411,7 +11399,7 @@
         <v>1</v>
       </c>
       <c r="V143" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="W143" s="1">
         <v>45219</v>
@@ -11479,7 +11467,7 @@
         <v>2</v>
       </c>
       <c r="V144" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="W144" s="1">
         <v>45219</v>
@@ -11547,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="V145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="W145" s="1">
         <v>45219</v>
@@ -11615,7 +11603,7 @@
         <v>2</v>
       </c>
       <c r="V146" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="W146" s="1">
         <v>45219</v>
@@ -11682,11 +11670,11 @@
       <c r="T147">
         <v>3</v>
       </c>
-      <c r="U147" t="s">
-        <v>132</v>
+      <c r="U147">
+        <v>2</v>
       </c>
       <c r="V147" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="W147" s="1">
         <v>45219</v>
@@ -11754,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="V148" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="W148" s="1">
         <v>45219</v>
@@ -11822,7 +11810,7 @@
         <v>4</v>
       </c>
       <c r="V149" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="W149" s="1">
         <v>45219</v>
@@ -11890,7 +11878,7 @@
         <v>2</v>
       </c>
       <c r="V150" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W150" s="1">
         <v>45219</v>
@@ -11958,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="V151" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="W151" s="1">
         <v>45219</v>
@@ -12025,11 +12013,11 @@
       <c r="T152">
         <v>12</v>
       </c>
-      <c r="U152" t="s">
-        <v>129</v>
+      <c r="U152">
+        <v>1</v>
       </c>
       <c r="V152" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="W152" s="1">
         <v>45219</v>
@@ -12097,7 +12085,7 @@
         <v>6</v>
       </c>
       <c r="V153" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="W153" s="1">
         <v>45219</v>
@@ -12164,11 +12152,11 @@
       <c r="T154">
         <v>1</v>
       </c>
-      <c r="U154" t="s">
-        <v>129</v>
+      <c r="U154">
+        <v>1</v>
       </c>
       <c r="V154" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="W154" s="1">
         <v>45219</v>
@@ -12236,7 +12224,7 @@
         <v>4</v>
       </c>
       <c r="V155" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="W155" s="1">
         <v>45219</v>
@@ -12304,7 +12292,7 @@
         <v>5</v>
       </c>
       <c r="V156" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="W156" s="1">
         <v>45219</v>
@@ -12372,7 +12360,7 @@
         <v>1</v>
       </c>
       <c r="V157" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="W157" s="1">
         <v>45140</v>
@@ -12440,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="V158" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="W158" s="1">
         <v>45140</v>
@@ -12508,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="V159" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="W159" s="1">
         <v>45140</v>
@@ -12576,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="V160" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="W160" s="1">
         <v>45140</v>
@@ -12644,7 +12632,7 @@
         <v>1</v>
       </c>
       <c r="V161" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="W161" s="1">
         <v>45140</v>
@@ -12712,7 +12700,7 @@
         <v>5</v>
       </c>
       <c r="V162" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="W162" s="1">
         <v>45139</v>
@@ -12780,7 +12768,7 @@
         <v>3</v>
       </c>
       <c r="V163" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="W163" s="1">
         <v>45133</v>
@@ -12848,7 +12836,7 @@
         <v>5</v>
       </c>
       <c r="V164" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="W164" s="1">
         <v>45140</v>
@@ -12916,7 +12904,7 @@
         <v>9</v>
       </c>
       <c r="V165" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="W165" s="1">
         <v>45133</v>
@@ -12984,7 +12972,7 @@
         <v>1</v>
       </c>
       <c r="V166" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="W166" s="1">
         <v>45133</v>
@@ -13052,7 +13040,7 @@
         <v>1</v>
       </c>
       <c r="V167" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="W167" s="1">
         <v>45133</v>
@@ -13120,7 +13108,7 @@
         <v>1</v>
       </c>
       <c r="V168" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="W168" s="1">
         <v>45133</v>
@@ -13188,7 +13176,7 @@
         <v>1</v>
       </c>
       <c r="V169" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="W169" s="1">
         <v>45164</v>
@@ -13256,7 +13244,7 @@
         <v>4</v>
       </c>
       <c r="V170" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="W170" s="1">
         <v>45133</v>
@@ -13317,11 +13305,11 @@
       <c r="T171">
         <v>3</v>
       </c>
-      <c r="U171" t="s">
-        <v>130</v>
+      <c r="U171">
+        <v>3</v>
       </c>
       <c r="V171" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="W171" s="1">
         <v>45124</v>
@@ -13389,7 +13377,7 @@
         <v>1</v>
       </c>
       <c r="V172" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="W172" s="1">
         <v>45124</v>
@@ -13457,7 +13445,7 @@
         <v>3</v>
       </c>
       <c r="V173" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="W173" s="1">
         <v>45124</v>
@@ -13525,7 +13513,7 @@
         <v>11</v>
       </c>
       <c r="V174" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="W174" s="1">
         <v>45124</v>
@@ -13593,7 +13581,7 @@
         <v>1</v>
       </c>
       <c r="V175" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="W175" s="1">
         <v>45139</v>
@@ -13661,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="V176" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="W176" s="1">
         <v>45139</v>
@@ -13729,7 +13717,7 @@
         <v>4</v>
       </c>
       <c r="V177" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="W177" s="1">
         <v>45139</v>
@@ -13797,7 +13785,7 @@
         <v>14</v>
       </c>
       <c r="V178" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="W178" s="1">
         <v>45164</v>
@@ -13865,7 +13853,7 @@
         <v>1</v>
       </c>
       <c r="V179" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="W179" s="1">
         <v>45164</v>
@@ -13933,7 +13921,7 @@
         <v>1</v>
       </c>
       <c r="V180" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="W180" s="1">
         <v>45164</v>
@@ -14000,11 +13988,11 @@
       <c r="T181">
         <v>3</v>
       </c>
-      <c r="U181" t="s">
-        <v>130</v>
+      <c r="U181">
+        <v>3</v>
       </c>
       <c r="V181" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="W181" s="1">
         <v>45164</v>
@@ -14072,7 +14060,7 @@
         <v>1</v>
       </c>
       <c r="V182" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="W182" s="1">
         <v>45165</v>
@@ -14140,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="V183" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="W183" s="1">
         <v>45165</v>
@@ -14208,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="V184" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="W184" s="1">
         <v>45120</v>
@@ -14276,7 +14264,7 @@
         <v>2</v>
       </c>
       <c r="V185" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="W185" s="1">
         <v>45120</v>
@@ -14344,7 +14332,7 @@
         <v>1</v>
       </c>
       <c r="V186" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="W186" s="1">
         <v>45120</v>
@@ -14412,7 +14400,7 @@
         <v>11</v>
       </c>
       <c r="V187" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="W187" s="1">
         <v>45133</v>
@@ -14480,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="V188" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="W188" s="1">
         <v>45164</v>
@@ -14548,7 +14536,7 @@
         <v>1</v>
       </c>
       <c r="V189" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="W189" s="1">
         <v>45164</v>
@@ -14616,7 +14604,7 @@
         <v>18</v>
       </c>
       <c r="V190" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="W190" s="1">
         <v>45120</v>
@@ -14684,7 +14672,7 @@
         <v>3</v>
       </c>
       <c r="V191" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="W191" s="1">
         <v>45121</v>
@@ -14752,7 +14740,7 @@
         <v>1</v>
       </c>
       <c r="V192" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="W192" s="1">
         <v>45133</v>
@@ -14820,7 +14808,7 @@
         <v>1</v>
       </c>
       <c r="V193" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="W193" s="1">
         <v>45120</v>
@@ -14888,7 +14876,7 @@
         <v>6</v>
       </c>
       <c r="V194" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="W194" s="1">
         <v>45139</v>
@@ -14956,7 +14944,7 @@
         <v>2</v>
       </c>
       <c r="V195" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="W195" s="1">
         <v>45119</v>
@@ -15024,7 +15012,7 @@
         <v>4</v>
       </c>
       <c r="V196" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="W196" s="1">
         <v>45119</v>
@@ -15092,7 +15080,7 @@
         <v>2</v>
       </c>
       <c r="V197" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="W197" s="1">
         <v>45120</v>
@@ -15160,7 +15148,7 @@
         <v>2</v>
       </c>
       <c r="V198" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="W198" s="1">
         <v>45121</v>
@@ -15228,7 +15216,7 @@
         <v>2</v>
       </c>
       <c r="V199" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="W199" s="1">
         <v>45120</v>
@@ -15296,7 +15284,7 @@
         <v>1</v>
       </c>
       <c r="V200" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="W200" s="1">
         <v>45120</v>
@@ -15364,7 +15352,7 @@
         <v>2</v>
       </c>
       <c r="V201" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="W201" s="1">
         <v>45121</v>
@@ -15432,7 +15420,7 @@
         <v>2</v>
       </c>
       <c r="V202" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="W202" s="1">
         <v>45077</v>
@@ -15500,7 +15488,7 @@
         <v>2</v>
       </c>
       <c r="V203" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="W203" s="1">
         <v>45219</v>
@@ -15568,7 +15556,7 @@
         <v>4</v>
       </c>
       <c r="V204" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="W204" s="1">
         <v>45119</v>
@@ -15636,7 +15624,7 @@
         <v>8</v>
       </c>
       <c r="V205" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="W205" s="1">
         <v>45133</v>
@@ -15704,7 +15692,7 @@
         <v>5</v>
       </c>
       <c r="V206" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="W206" s="1">
         <v>45133</v>
@@ -15772,7 +15760,7 @@
         <v>2</v>
       </c>
       <c r="V207" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="W207" s="1">
         <v>45513</v>
@@ -15840,7 +15828,7 @@
         <v>1</v>
       </c>
       <c r="V208" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="W208" s="1">
         <v>45165</v>
@@ -15908,7 +15896,7 @@
         <v>1</v>
       </c>
       <c r="V209" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="W209" s="1">
         <v>45121</v>
@@ -15976,7 +15964,7 @@
         <v>1</v>
       </c>
       <c r="V210" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="W210" s="1">
         <v>45139</v>
@@ -16044,7 +16032,7 @@
         <v>2</v>
       </c>
       <c r="V211" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="W211" s="1">
         <v>45077</v>
@@ -16112,7 +16100,7 @@
         <v>1</v>
       </c>
       <c r="V212" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="W212" s="1">
         <v>45262</v>
@@ -16180,7 +16168,7 @@
         <v>3</v>
       </c>
       <c r="V213" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="W213" s="1">
         <v>45068</v>
@@ -16248,7 +16236,7 @@
         <v>1</v>
       </c>
       <c r="V214" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="W214" s="1">
         <v>45165</v>
@@ -16316,7 +16304,7 @@
         <v>1</v>
       </c>
       <c r="V215" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="W215" s="1">
         <v>45164</v>
@@ -16384,7 +16372,7 @@
         <v>16</v>
       </c>
       <c r="V216" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="W216" s="1">
         <v>45119</v>
@@ -16452,7 +16440,7 @@
         <v>1</v>
       </c>
       <c r="V217" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="W217" s="1">
         <v>45164</v>
@@ -16520,7 +16508,7 @@
         <v>1</v>
       </c>
       <c r="V218" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="W218" s="1">
         <v>45052</v>
@@ -16588,7 +16576,7 @@
         <v>2</v>
       </c>
       <c r="V219" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="W219" s="1">
         <v>45632</v>
@@ -16656,7 +16644,7 @@
         <v>3</v>
       </c>
       <c r="V220" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="W220" s="1">
         <v>45632</v>
@@ -16724,7 +16712,7 @@
         <v>19</v>
       </c>
       <c r="V221" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="W221" s="1">
         <v>45807</v>
@@ -16792,7 +16780,7 @@
         <v>1</v>
       </c>
       <c r="V222" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="W222" s="1">
         <v>45608</v>
@@ -16860,7 +16848,7 @@
         <v>2</v>
       </c>
       <c r="V223" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="W223" s="1">
         <v>45031</v>
@@ -16928,7 +16916,7 @@
         <v>2</v>
       </c>
       <c r="V224" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="W224" s="1">
         <v>45031</v>
@@ -16996,7 +16984,7 @@
         <v>3</v>
       </c>
       <c r="V225" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="W225" s="1">
         <v>45031</v>
@@ -17064,7 +17052,7 @@
         <v>1</v>
       </c>
       <c r="V226" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="W226" s="1">
         <v>45031</v>
@@ -17132,7 +17120,7 @@
         <v>1</v>
       </c>
       <c r="V227" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="W227" s="1">
         <v>45030</v>
@@ -17200,7 +17188,7 @@
         <v>2</v>
       </c>
       <c r="V228" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="W228" s="1">
         <v>45047</v>
@@ -17268,7 +17256,7 @@
         <v>1</v>
       </c>
       <c r="V229" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="W229" s="1">
         <v>44987</v>
@@ -17335,11 +17323,11 @@
       <c r="T230">
         <v>1</v>
       </c>
-      <c r="U230" t="s">
-        <v>129</v>
+      <c r="U230">
+        <v>1</v>
       </c>
       <c r="V230" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="W230" s="1">
         <v>44987</v>
@@ -17407,7 +17395,7 @@
         <v>1</v>
       </c>
       <c r="V231" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="W231" s="1">
         <v>44987</v>
@@ -17475,7 +17463,7 @@
         <v>1</v>
       </c>
       <c r="V232" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="W232" s="1">
         <v>44987</v>
@@ -17543,7 +17531,7 @@
         <v>3</v>
       </c>
       <c r="V233" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="W233" s="1">
         <v>44980</v>
@@ -17611,7 +17599,7 @@
         <v>2</v>
       </c>
       <c r="V234" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="W234" s="1">
         <v>44983</v>
@@ -17679,7 +17667,7 @@
         <v>3</v>
       </c>
       <c r="V235" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="W235" s="1">
         <v>44983</v>
@@ -17747,7 +17735,7 @@
         <v>1</v>
       </c>
       <c r="V236" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="W236" s="1">
         <v>44982</v>
@@ -17815,7 +17803,7 @@
         <v>1</v>
       </c>
       <c r="V237" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="W237" s="1">
         <v>44890</v>
@@ -17883,7 +17871,7 @@
         <v>1</v>
       </c>
       <c r="V238" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="W238" s="1">
         <v>44890</v>
@@ -17951,7 +17939,7 @@
         <v>2</v>
       </c>
       <c r="V239" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="W239" s="1">
         <v>45010</v>
@@ -18019,7 +18007,7 @@
         <v>2</v>
       </c>
       <c r="V240" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W240" s="1">
         <v>44890</v>
@@ -18087,7 +18075,7 @@
         <v>1</v>
       </c>
       <c r="V241" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W241" s="1">
         <v>44890</v>
@@ -18155,7 +18143,7 @@
         <v>1</v>
       </c>
       <c r="V242" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W242" s="1">
         <v>45010</v>
@@ -18223,7 +18211,7 @@
         <v>1</v>
       </c>
       <c r="V243" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W243" s="1">
         <v>44890</v>
@@ -18291,7 +18279,7 @@
         <v>1</v>
       </c>
       <c r="V244" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="W244" s="1">
         <v>44893</v>
@@ -18359,7 +18347,7 @@
         <v>3</v>
       </c>
       <c r="V245" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="W245" s="1">
         <v>44846</v>
@@ -18427,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="V246" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="W246" s="1">
         <v>44846</v>
@@ -18495,7 +18483,7 @@
         <v>2</v>
       </c>
       <c r="V247" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="W247" s="1">
         <v>44791</v>
@@ -18563,7 +18551,7 @@
         <v>1</v>
       </c>
       <c r="V248" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="W248" s="1">
         <v>44752</v>
@@ -18631,7 +18619,7 @@
         <v>6</v>
       </c>
       <c r="V249" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="W249" s="1">
         <v>44756</v>
@@ -18699,7 +18687,7 @@
         <v>1</v>
       </c>
       <c r="V250" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W250" s="1">
         <v>44737</v>
@@ -18767,7 +18755,7 @@
         <v>4</v>
       </c>
       <c r="V251" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W251" s="1">
         <v>44755</v>
@@ -18835,7 +18823,7 @@
         <v>6</v>
       </c>
       <c r="V252" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W252" s="1">
         <v>44756</v>
@@ -18903,7 +18891,7 @@
         <v>1</v>
       </c>
       <c r="V253" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W253" s="1">
         <v>44637</v>
@@ -18971,7 +18959,7 @@
         <v>1</v>
       </c>
       <c r="V254" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="W254" s="1">
         <v>44637</v>
@@ -19039,7 +19027,7 @@
         <v>1</v>
       </c>
       <c r="V255" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="W255" s="1">
         <v>44637</v>
@@ -19107,7 +19095,7 @@
         <v>1</v>
       </c>
       <c r="V256" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="W256" s="1">
         <v>44637</v>
@@ -19175,7 +19163,7 @@
         <v>1</v>
       </c>
       <c r="V257" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="W257" s="1">
         <v>44617</v>
@@ -19243,7 +19231,7 @@
         <v>4</v>
       </c>
       <c r="V258" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="W258" s="1">
         <v>44992</v>
@@ -19311,7 +19299,7 @@
         <v>1</v>
       </c>
       <c r="V259" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="W259" s="1">
         <v>44992</v>
@@ -19379,7 +19367,7 @@
         <v>1</v>
       </c>
       <c r="V260" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="W260" s="1">
         <v>44578</v>
@@ -19447,7 +19435,7 @@
         <v>2</v>
       </c>
       <c r="V261" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="W261" s="1">
         <v>44578</v>
@@ -19515,7 +19503,7 @@
         <v>17</v>
       </c>
       <c r="V262" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="W262" s="1">
         <v>44474</v>
@@ -19583,7 +19571,7 @@
         <v>1</v>
       </c>
       <c r="V263" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="W263" s="1">
         <v>44474</v>
@@ -19651,7 +19639,7 @@
         <v>1</v>
       </c>
       <c r="V264" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="W264" s="1">
         <v>44474</v>
@@ -19719,7 +19707,7 @@
         <v>1</v>
       </c>
       <c r="V265" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="W265" s="1">
         <v>44474</v>
@@ -19787,7 +19775,7 @@
         <v>2</v>
       </c>
       <c r="V266" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="W266" s="1">
         <v>44474</v>
@@ -19855,7 +19843,7 @@
         <v>1</v>
       </c>
       <c r="V267" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="W267" s="1">
         <v>44474</v>
@@ -19923,7 +19911,7 @@
         <v>1</v>
       </c>
       <c r="V268" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="W268" s="1">
         <v>44474</v>
@@ -19991,7 +19979,7 @@
         <v>1</v>
       </c>
       <c r="V269" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="W269" s="1">
         <v>44474</v>
@@ -20059,7 +20047,7 @@
         <v>1</v>
       </c>
       <c r="V270" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="W270" s="1">
         <v>44474</v>
@@ -20127,7 +20115,7 @@
         <v>1</v>
       </c>
       <c r="V271" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="W271" s="1">
         <v>44474</v>
@@ -20195,7 +20183,7 @@
         <v>1</v>
       </c>
       <c r="V272" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="W272" s="1">
         <v>44474</v>
@@ -20263,7 +20251,7 @@
         <v>1</v>
       </c>
       <c r="V273" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="W273" s="1">
         <v>44474</v>
@@ -20331,7 +20319,7 @@
         <v>1</v>
       </c>
       <c r="V274" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="W274" s="1">
         <v>44371</v>
@@ -20399,7 +20387,7 @@
         <v>1</v>
       </c>
       <c r="V275" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="W275" s="1">
         <v>44474</v>
@@ -20466,11 +20454,11 @@
       <c r="T276">
         <v>1</v>
       </c>
-      <c r="U276" t="s">
-        <v>129</v>
+      <c r="U276">
+        <v>1</v>
       </c>
       <c r="V276" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="W276" s="1">
         <v>44474</v>
@@ -20538,7 +20526,7 @@
         <v>1</v>
       </c>
       <c r="V277" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="W277" s="1">
         <v>44149</v>
@@ -20606,7 +20594,7 @@
         <v>2</v>
       </c>
       <c r="V278" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="W278" s="1">
         <v>44141</v>
@@ -20674,7 +20662,7 @@
         <v>1</v>
       </c>
       <c r="V279" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="W279" s="1">
         <v>44141</v>
@@ -20742,7 +20730,7 @@
         <v>2</v>
       </c>
       <c r="V280" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="W280" s="1">
         <v>44133</v>
@@ -20810,7 +20798,7 @@
         <v>5</v>
       </c>
       <c r="V281" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="W281" s="1">
         <v>44127</v>
@@ -20878,7 +20866,7 @@
         <v>1</v>
       </c>
       <c r="V282" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="W282" s="1">
         <v>44474</v>
@@ -20946,7 +20934,7 @@
         <v>3</v>
       </c>
       <c r="V283" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="W283" s="1">
         <v>44109</v>
@@ -21014,7 +21002,7 @@
         <v>7</v>
       </c>
       <c r="V284" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="W284" s="1">
         <v>44474</v>
@@ -21082,7 +21070,7 @@
         <v>1</v>
       </c>
       <c r="V285" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="W285" s="1">
         <v>44098</v>
@@ -21150,7 +21138,7 @@
         <v>1</v>
       </c>
       <c r="V286" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="W286" s="1">
         <v>44090</v>
@@ -21218,7 +21206,7 @@
         <v>3</v>
       </c>
       <c r="V287" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="W287" s="1">
         <v>44090</v>
@@ -21286,7 +21274,7 @@
         <v>1</v>
       </c>
       <c r="V288" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="W288" s="1">
         <v>44090</v>
@@ -21354,7 +21342,7 @@
         <v>1</v>
       </c>
       <c r="V289" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="W289" s="1">
         <v>44088</v>
@@ -21422,7 +21410,7 @@
         <v>6</v>
       </c>
       <c r="V290" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="W290" s="1">
         <v>44474</v>
@@ -21490,7 +21478,7 @@
         <v>1</v>
       </c>
       <c r="V291" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="W291" s="1">
         <v>44474</v>
